--- a/inv/women_belts.xlsx
+++ b/inv/women_belts.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="150" windowWidth="16215" windowHeight="8970"/>
+    <workbookView xWindow="240" yWindow="540" windowWidth="22695" windowHeight="9915"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,42 +16,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>Title</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>titleid</t>
   </si>
   <si>
-    <t>women_footwear</t>
-  </si>
-  <si>
-    <t>Women Footwear</t>
-  </si>
-  <si>
-    <t>women_wallers</t>
-  </si>
-  <si>
-    <t>Women Wallets</t>
-  </si>
-  <si>
-    <t>women_belts</t>
-  </si>
-  <si>
-    <t>Women Belts</t>
-  </si>
-  <si>
-    <t>women_bags</t>
-  </si>
-  <si>
-    <t>Women Bags</t>
-  </si>
-  <si>
-    <t>women_jewellery</t>
-  </si>
-  <si>
-    <t>Women Jewellery</t>
+    <t>title</t>
+  </si>
+  <si>
+    <t>women_belts_leather</t>
+  </si>
+  <si>
+    <t>Women Leather Belts</t>
+  </si>
+  <si>
+    <t>?page=women_leather_belts</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>scat</t>
   </si>
 </sst>
 </file>
@@ -63,7 +51,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -94,7 +81,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
 </styleSheet>
 </file>
 
@@ -383,55 +370,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
